--- a/InputData/hydgn/HPS/Hydrogen Production Shareweights.xlsx
+++ b/InputData/hydgn/HPS/Hydrogen Production Shareweights.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\hydgn\HPS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\hydgn\HPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7090C818-F3C4-450C-8193-71E4BC5E7E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9D97BE-8AE0-479C-8FF6-DFEFB3B6E3B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="728" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="728" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>Source:</t>
   </si>
@@ -54,9 +56,6 @@
   </si>
   <si>
     <t>Interpolation Method</t>
-  </si>
-  <si>
-    <t>Max Fraction of Production (dimensionless)</t>
   </si>
   <si>
     <t>*for passenger LDVs only, see Assumptions page</t>
@@ -138,6 +137,42 @@
   </si>
   <si>
     <t>HPS Hydrogen Production Shareweights</t>
+  </si>
+  <si>
+    <t>Shareweight (dimensionless)</t>
+  </si>
+  <si>
+    <t>Judgment values (no external source). Shape: the sigmoid interpolation sheet copied from the vehicle 'Max Potential Sales Share' workbook (Data tab, L/k/Xo in I2:I4).</t>
+  </si>
+  <si>
+    <t>Green (electrolysis with guaranteed clean electricity) = blue (natural gas reforming with CCS) since 2026-10-26: Data!D15:F15 = D16:F16, so both rows follow the same S-curve to 0.25 (2035 'max').</t>
+  </si>
+  <si>
+    <t>Evidence used for the green = blue choice (announced and committed US low-carbon hydrogen is blue-heavy by output):</t>
+  </si>
+  <si>
+    <t>- BloombergNEF, 'US Clean Hydrogen Market Outlook' (P. Kaur), data as of 2025-07-28, slide 10, via California Energy Commission docket TN 265044 (efiling.energy.ca.gov/GetDocument.aspx?tn=265044): announced US low-carbon H2 ~11.7 Mt/yr blue vs ~3.8 Mt/yr green (~76% / 24% of 15.5 Mt/yr). VERIFIED in source; series labels inferred from the slide.</t>
+  </si>
+  <si>
+    <t>- US DOE, Pathways to Commercial Liftoff: Clean Hydrogen, Jan 2025 update: ~14 MMTpa announced, ~60% reforming+CCS / ~40% electrolysis. SECONDARY (pv-magazine-usa.com, 2025-01-22); DOE PDF not opened.</t>
+  </si>
+  <si>
+    <t>- IEA, Global Hydrogen Review 2025 (Sep 2025), ch. 3: US FIDs/construction are mainly CCUS-based (CF Industries Yazoo City retrofit FID 2024, Blue Point FID 2025, Linde Beaumont capture due 2026); one US electrolysis-type FID in 2025 to end-July (Roadrunner). VERIFIED in source (IEA PDF).</t>
+  </si>
+  <si>
+    <t>- OBBBA (2025): 45V requires construction start before 2028-01-01 (IEA GHR-25, VERIFIED); 2025-26 cancellations hit both grades - Rhodium/Clean Investment Monitor reports cancelled H2 investment mostly green; Air Products Louisiana blue cancelled, ExxonMobil Baytown blue halted. SECONDARY (Latitude Media 2026-05-20; Energy Intelligence 2026-06-30; IIR 2026-07-23).</t>
+  </si>
+  <si>
+    <t>These are soft logit shareweights, not caps (the old 'Max Potential Sales Share' label is inherited from the vehicle sheet). Shares follow share ~ HPS x exp(-0.2 x cost in $/MMBtu): a 3x weight is worth ~$5.5/MMBtu (~$0.74/kg).</t>
+  </si>
+  <si>
+    <t>History: Mar 2025 (commits 2bb87fbc, 8baf6fc7, in-progress hydrogen structure) set green 0.75 and blue 0.25 (3:1) with no documented basis. That implied green took ~50-60% of new low carbon capacity in 2028-2030, against the blue-heavy evidence above.</t>
+  </si>
+  <si>
+    <t>2026-10-26 (Dan O'Brien, B25 in Hydrogen_Options_Plan.md): green set equal to blue; blue, grey and other pathways unchanged, so the BAU blue/grey split in the 'other' tier is unchanged. Since B24 these weights also set the low carbon hydrogen price (new-build logit-share weighted).</t>
+  </si>
+  <si>
+    <t>This remains a judgment that needs review: refresh against the IEA Hydrogen Production and Infrastructure Projects database (not accessible when written) and FID-stage capacity by technology. Post-2040 shares rest on cost assumptions, not project evidence.</t>
   </si>
 </sst>
 </file>
@@ -1361,6 +1396,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1368,7 +1404,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1580,88 +1615,88 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2" formatCode="General">
-                  <c:v>1.9947745182649392E-2</c:v>
+                  <c:v>6.6492483942164641E-3</c:v>
                 </c:pt>
                 <c:pt idx="3" formatCode="General">
-                  <c:v>2.9374292097573265E-2</c:v>
+                  <c:v>9.791430699191089E-3</c:v>
                 </c:pt>
                 <c:pt idx="4" formatCode="General">
-                  <c:v>4.2993131924151544E-2</c:v>
+                  <c:v>1.4331043974717182E-2</c:v>
                 </c:pt>
                 <c:pt idx="5" formatCode="General">
-                  <c:v>6.237952237044176E-2</c:v>
+                  <c:v>2.0793174123480588E-2</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="General">
-                  <c:v>8.9402191516588167E-2</c:v>
+                  <c:v>2.9800730505529387E-2</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="General">
-                  <c:v>0.12598621114955663</c:v>
+                  <c:v>4.199540371651888E-2</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
-                  <c:v>0.17360641237573674</c:v>
+                  <c:v>5.7868804125245581E-2</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="General">
-                  <c:v>0.23251913915429065</c:v>
+                  <c:v>7.7506379718096888E-2</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
-                  <c:v>0.300984254915661</c:v>
+                  <c:v>0.100328084971887</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="General">
-                  <c:v>0.375</c:v>
+                  <c:v>0.125</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>0.449015745084339</c:v>
+                  <c:v>0.149671915028113</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>0.51748086084570932</c:v>
+                  <c:v>0.17249362028190313</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>0.57639358762426329</c:v>
+                  <c:v>0.19213119587475444</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>0.62401378885044334</c:v>
+                  <c:v>0.20800459628348111</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>0.66059780848341176</c:v>
+                  <c:v>0.22019926949447058</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>0.68762047762955825</c:v>
+                  <c:v>0.22920682587651942</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>0.70700686807584845</c:v>
+                  <c:v>0.23566895602528282</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>0.72062570790242675</c:v>
+                  <c:v>0.24020856930080892</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>0.73005225481735059</c:v>
+                  <c:v>0.24335075160578351</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>0.73651034252843128</c:v>
+                  <c:v>0.24550344750947711</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>0.74090367376179433</c:v>
+                  <c:v>0.24696789125393143</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>0.74387807163513009</c:v>
+                  <c:v>0.24795935721171003</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>0.74588527582541209</c:v>
+                  <c:v>0.24862842527513737</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>0.74723682007542302</c:v>
+                  <c:v>0.24907894002514103</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>0.74814553263252404</c:v>
+                  <c:v>0.24938184421084134</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="General">
-                  <c:v>0.74875589918986918</c:v>
+                  <c:v>0.24958529972995638</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="General">
-                  <c:v>0.74916559797535487</c:v>
+                  <c:v>0.24972186599178495</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="General">
-                  <c:v>0.74944047837462258</c:v>
+                  <c:v>0.24981349279154083</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1802,6 +1837,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1809,7 +1845,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3324,29 +3359,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="56.26953125" customWidth="1"/>
+    <col min="2" max="2" width="56.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="8"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
       <c r="B5" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3361,51 +3449,51 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:AL16"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.26953125" customWidth="1"/>
-    <col min="2" max="2" width="18.81640625" customWidth="1"/>
-    <col min="3" max="3" width="24.1796875" customWidth="1"/>
-    <col min="4" max="4" width="14.7265625" customWidth="1"/>
-    <col min="5" max="5" width="16.26953125" customWidth="1"/>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="18" style="5" customWidth="1"/>
-    <col min="7" max="7" width="13.1796875" customWidth="1"/>
-    <col min="8" max="9" width="9.1796875" customWidth="1"/>
-    <col min="14" max="14" width="11.1796875" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I1" s="10"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
       <c r="L1" s="11"/>
       <c r="N1" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O1" s="10"/>
       <c r="P1" s="11"/>
       <c r="Q1" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R1" s="10"/>
       <c r="T1" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U1" s="10"/>
       <c r="W1" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X1" s="10"/>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>3</v>
@@ -3438,9 +3526,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>4</v>
@@ -3473,9 +3561,9 @@
         <v>-0.4</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>5</v>
@@ -3508,12 +3596,12 @@
         <v>-10.5</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:38" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3528,13 +3616,13 @@
         <v>6</v>
       </c>
       <c r="N6" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O6" s="15">
         <v>9.9000000000000005E-2</v>
       </c>
       <c r="R6" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="S6">
         <v>0.05</v>
@@ -3555,11 +3643,11 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:38" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="8"/>
       <c r="B7" s="8"/>
       <c r="C7" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="2">
@@ -3570,13 +3658,13 @@
       </c>
       <c r="G7" s="2"/>
       <c r="N7" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O7">
         <v>1.8679140068700261E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="87" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:38" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -3584,18 +3672,18 @@
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
       <c r="G8" s="17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="D9" s="8">
         <v>2021</v>
@@ -3727,15 +3815,15 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10">
         <v>0.05</v>
@@ -3871,9 +3959,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -3889,7 +3977,7 @@
         <v>n/a</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" ref="I11:I16" si="2">E11</f>
+        <f t="shared" ref="I11:I13" si="2">E11</f>
         <v>1</v>
       </c>
       <c r="J11">
@@ -4009,9 +4097,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -4147,9 +4235,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -4285,9 +4373,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -4423,18 +4511,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D15">
+        <f>D16</f>
         <v>0</v>
       </c>
       <c r="E15" s="24">
+        <f>E16</f>
         <v>0</v>
       </c>
       <c r="F15" s="26">
-        <v>0.75</v>
+        <f>F16</f>
+        <v>0.25</v>
       </c>
       <c r="G15" s="5" t="str">
         <f>IF(E15=F15,"n/a",IF(OR(C15="electrolysis with guaranteed clean electricity",C15="natural gas reforming with CCS"),"s-curve","linear"))</f>
@@ -4450,122 +4541,122 @@
       </c>
       <c r="K15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:K$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,K$9))</f>
-        <v>1.9947745182649392E-2</v>
+        <v>6.6492483942164641E-3</v>
       </c>
       <c r="L15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:L$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,L$9))</f>
-        <v>2.9374292097573265E-2</v>
+        <v>9.791430699191089E-3</v>
       </c>
       <c r="M15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:M$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,M$9))</f>
-        <v>4.2993131924151544E-2</v>
+        <v>1.4331043974717182E-2</v>
       </c>
       <c r="N15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:N$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,N$9))</f>
-        <v>6.237952237044176E-2</v>
+        <v>2.0793174123480588E-2</v>
       </c>
       <c r="O15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:O$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,O$9))</f>
-        <v>8.9402191516588167E-2</v>
+        <v>2.9800730505529387E-2</v>
       </c>
       <c r="P15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:P$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,P$9))</f>
-        <v>0.12598621114955663</v>
+        <v>4.199540371651888E-2</v>
       </c>
       <c r="Q15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:Q$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,Q$9))</f>
-        <v>0.17360641237573674</v>
+        <v>5.7868804125245581E-2</v>
       </c>
       <c r="R15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:R$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,R$9))</f>
-        <v>0.23251913915429065</v>
+        <v>7.7506379718096888E-2</v>
       </c>
       <c r="S15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:S$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,S$9))</f>
-        <v>0.300984254915661</v>
+        <v>0.100328084971887</v>
       </c>
       <c r="T15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:T$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,T$9))</f>
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="U15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:U$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,U$9))</f>
-        <v>0.449015745084339</v>
+        <v>0.149671915028113</v>
       </c>
       <c r="V15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:V$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,V$9))</f>
-        <v>0.51748086084570932</v>
+        <v>0.17249362028190313</v>
       </c>
       <c r="W15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:W$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,W$9))</f>
-        <v>0.57639358762426329</v>
+        <v>0.19213119587475444</v>
       </c>
       <c r="X15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:X$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,X$9))</f>
-        <v>0.62401378885044334</v>
+        <v>0.20800459628348111</v>
       </c>
       <c r="Y15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:Y$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,Y$9))</f>
-        <v>0.66059780848341176</v>
+        <v>0.22019926949447058</v>
       </c>
       <c r="Z15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:Z$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,Z$9))</f>
-        <v>0.68762047762955825</v>
+        <v>0.22920682587651942</v>
       </c>
       <c r="AA15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AA$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AA$9))</f>
-        <v>0.70700686807584845</v>
+        <v>0.23566895602528282</v>
       </c>
       <c r="AB15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AB$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AB$9))</f>
-        <v>0.72062570790242675</v>
+        <v>0.24020856930080892</v>
       </c>
       <c r="AC15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AC$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AC$9))</f>
-        <v>0.73005225481735059</v>
+        <v>0.24335075160578351</v>
       </c>
       <c r="AD15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AD$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AD$9))</f>
-        <v>0.73651034252843128</v>
+        <v>0.24550344750947711</v>
       </c>
       <c r="AE15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AE$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AE$9))</f>
-        <v>0.74090367376179433</v>
+        <v>0.24696789125393143</v>
       </c>
       <c r="AF15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AF$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AF$9))</f>
-        <v>0.74387807163513009</v>
+        <v>0.24795935721171003</v>
       </c>
       <c r="AG15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AG$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AG$9))</f>
-        <v>0.74588527582541209</v>
+        <v>0.24862842527513737</v>
       </c>
       <c r="AH15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AH$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AH$9))</f>
-        <v>0.74723682007542302</v>
+        <v>0.24907894002514103</v>
       </c>
       <c r="AI15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AI$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AI$9))</f>
-        <v>0.74814553263252404</v>
+        <v>0.24938184421084134</v>
       </c>
       <c r="AJ15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AJ$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AJ$9))</f>
-        <v>0.74875589918986918</v>
+        <v>0.24958529972995638</v>
       </c>
       <c r="AK15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AK$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AK$9))</f>
-        <v>0.74916559797535487</v>
+        <v>0.24972186599178495</v>
       </c>
       <c r="AL15">
         <f>IF($G15="s-curve",$E15+($F15-$E15)*$I$2/(1+EXP($I$3*(COUNT($J$9:AL$9)+$I$4))),TREND($E15:$F15,$E$9:$F$9,AL$9))</f>
-        <v>0.74944047837462258</v>
+        <v>0.24981349279154083</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D16" s="22">
         <v>0</v>
@@ -4714,15 +4805,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.453125" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B1" s="18">
         <v>2021</v>
@@ -4844,9 +4935,9 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="20">
         <f>Data!I10</f>
@@ -4969,9 +5060,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="20">
         <f>Data!I11</f>
@@ -5094,9 +5185,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="20">
         <f>Data!I12</f>
@@ -5219,9 +5310,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="20">
         <f>Data!I13</f>
@@ -5344,9 +5435,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="20">
         <f>Data!I14</f>
@@ -5469,9 +5560,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="20">
         <f>Data!I15</f>
@@ -5483,120 +5574,120 @@
       </c>
       <c r="D7" s="20">
         <f>Data!K15</f>
-        <v>1.9947745182649392E-2</v>
+        <v>6.6492483942164641E-3</v>
       </c>
       <c r="E7" s="20">
         <f>Data!L15</f>
-        <v>2.9374292097573265E-2</v>
+        <v>9.791430699191089E-3</v>
       </c>
       <c r="F7" s="20">
         <f>Data!M15</f>
-        <v>4.2993131924151544E-2</v>
+        <v>1.4331043974717182E-2</v>
       </c>
       <c r="G7" s="20">
         <f>Data!N15</f>
-        <v>6.237952237044176E-2</v>
+        <v>2.0793174123480588E-2</v>
       </c>
       <c r="H7" s="20">
         <f>Data!O15</f>
-        <v>8.9402191516588167E-2</v>
+        <v>2.9800730505529387E-2</v>
       </c>
       <c r="I7" s="20">
         <f>Data!P15</f>
-        <v>0.12598621114955663</v>
+        <v>4.199540371651888E-2</v>
       </c>
       <c r="J7" s="20">
         <f>Data!Q15</f>
-        <v>0.17360641237573674</v>
+        <v>5.7868804125245581E-2</v>
       </c>
       <c r="K7" s="20">
         <f>Data!R15</f>
-        <v>0.23251913915429065</v>
+        <v>7.7506379718096888E-2</v>
       </c>
       <c r="L7" s="20">
         <f>Data!S15</f>
-        <v>0.300984254915661</v>
+        <v>0.100328084971887</v>
       </c>
       <c r="M7" s="20">
         <f>Data!T15</f>
-        <v>0.375</v>
+        <v>0.125</v>
       </c>
       <c r="N7" s="20">
         <f>Data!U15</f>
-        <v>0.449015745084339</v>
+        <v>0.149671915028113</v>
       </c>
       <c r="O7" s="20">
         <f>Data!V15</f>
-        <v>0.51748086084570932</v>
+        <v>0.17249362028190313</v>
       </c>
       <c r="P7" s="20">
         <f>Data!W15</f>
-        <v>0.57639358762426329</v>
+        <v>0.19213119587475444</v>
       </c>
       <c r="Q7" s="20">
         <f>Data!X15</f>
-        <v>0.62401378885044334</v>
+        <v>0.20800459628348111</v>
       </c>
       <c r="R7" s="20">
         <f>Data!Y15</f>
-        <v>0.66059780848341176</v>
+        <v>0.22019926949447058</v>
       </c>
       <c r="S7" s="20">
         <f>Data!Z15</f>
-        <v>0.68762047762955825</v>
+        <v>0.22920682587651942</v>
       </c>
       <c r="T7" s="20">
         <f>Data!AA15</f>
-        <v>0.70700686807584845</v>
+        <v>0.23566895602528282</v>
       </c>
       <c r="U7" s="20">
         <f>Data!AB15</f>
-        <v>0.72062570790242675</v>
+        <v>0.24020856930080892</v>
       </c>
       <c r="V7" s="20">
         <f>Data!AC15</f>
-        <v>0.73005225481735059</v>
+        <v>0.24335075160578351</v>
       </c>
       <c r="W7" s="20">
         <f>Data!AD15</f>
-        <v>0.73651034252843128</v>
+        <v>0.24550344750947711</v>
       </c>
       <c r="X7" s="20">
         <f>Data!AE15</f>
-        <v>0.74090367376179433</v>
+        <v>0.24696789125393143</v>
       </c>
       <c r="Y7" s="20">
         <f>Data!AF15</f>
-        <v>0.74387807163513009</v>
+        <v>0.24795935721171003</v>
       </c>
       <c r="Z7" s="20">
         <f>Data!AG15</f>
-        <v>0.74588527582541209</v>
+        <v>0.24862842527513737</v>
       </c>
       <c r="AA7" s="20">
         <f>Data!AH15</f>
-        <v>0.74723682007542302</v>
+        <v>0.24907894002514103</v>
       </c>
       <c r="AB7" s="20">
         <f>Data!AI15</f>
-        <v>0.74814553263252404</v>
+        <v>0.24938184421084134</v>
       </c>
       <c r="AC7" s="20">
         <f>Data!AJ15</f>
-        <v>0.74875589918986918</v>
+        <v>0.24958529972995638</v>
       </c>
       <c r="AD7" s="20">
         <f>Data!AK15</f>
-        <v>0.74916559797535487</v>
+        <v>0.24972186599178495</v>
       </c>
       <c r="AE7" s="20">
         <f>Data!AL15</f>
-        <v>0.74944047837462258</v>
+        <v>0.24981349279154083</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="20">
         <f>Data!I16</f>
